--- a/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/01_OLG1 - Sevkiyat ve Müşteri Alarmı/EKG-LOJ-FRM-08_sevkiyat_kilometre_taslari_ve_musteri_alarm_bildirim_ka.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/14_Çıkış Lojistiği ve Ambalaj/01_OLG1 - Sevkiyat ve Müşteri Alarmı/EKG-LOJ-FRM-08_sevkiyat_kilometre_taslari_ve_musteri_alarm_bildirim_ka.xlsx
@@ -855,7 +855,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Sevkiyat Kilometre Taşları ve Müşteri Alarm Bildirim Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Sevkiyat ve alarm takibi plan/fiilî tarih, ETA, bildirim, aksiyon ve kapanış kaydıyla sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1013,7 +1014,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-FRM-08&amp;C&amp;"Arial,Regular"&amp;11Sevkiyat Kilometre Taşları ve Müşteri Alarm Bildirim Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 25.09.2026
+Revizyon nedeni: Sevkiyat ve alarm takibi plan/fiilî tarih, ETA, bildirim, aksiyon ve kapanış kaydıyla sadeleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>